--- a/docs/schedule-recovery/スケジュール遅延リカバリ計画_テンプレート.xlsx
+++ b/docs/schedule-recovery/スケジュール遅延リカバリ計画_テンプレート.xlsx
@@ -1930,7 +1930,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>遅延しているタスクを洗い出します。当初日程と実績／見込日程を入れると「遅延日数」は自動計算されます。1行目は記入例です（提出前に削除）。</t>
+          <t>遅延しているタスクを洗い出します。当初日程と実績／見込日程を入れると「遅延日数」（暦日。土日・休日も数えます）は自動計算されます。1行目は記入例です（提出前に削除）。</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>遅延日数</t>
+          <t>遅延日数（暦日）</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
